--- a/public/files/akademik/template_matakuliah.xlsx
+++ b/public/files/akademik/template_matakuliah.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DELL\PhpstormProjects\sister_uij\public\files\akademik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523CBD61-AB52-4EFA-846B-65D80A916AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0F0623-E4A8-460D-906A-6E08AD838949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{22898463-E478-4D37-8126-113B27360583}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{22898463-E478-4D37-8126-113B27360583}"/>
   </bookViews>
   <sheets>
     <sheet name="Matakuliah" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -94,22 +96,22 @@
     <t>Semester</t>
   </si>
   <si>
+    <t>nama_matakuliah</t>
+  </si>
+  <si>
+    <t>semester</t>
+  </si>
+  <si>
+    <t>kd_jenis_matakuliah</t>
+  </si>
+  <si>
+    <t>kd_jenis_pelaksanaan</t>
+  </si>
+  <si>
     <t>kode_matakuliah</t>
   </si>
   <si>
-    <t>nama_matakuliah</t>
-  </si>
-  <si>
     <t>jumlah_sks</t>
-  </si>
-  <si>
-    <t>semester</t>
-  </si>
-  <si>
-    <t>kd_jenis_matakuliah</t>
-  </si>
-  <si>
-    <t>kd_jenis_pelaksanaan</t>
   </si>
 </sst>
 </file>
@@ -510,38 +512,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A58BF7-90DB-480B-B027-BC88F3BE8929}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="21.90625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7KXEcDvXMpfIe3infQBTbWyfUngqDkiPr6f1dn9FFOZ1FDHJnP16NHfRih13m8szAeLqfe0Nfe+zaoGT/qDfGg==" saltValue="S+Oe+ulAiAHkg6l7D7WHFg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Md4POHYHvlPBn0Z2BaEkiErs+lFDdnUFivJAeILqJBeLXykN2g0mpURlIqHpTLD82jD58ii3a8WMGmMWjHt+Uw==" saltValue="vkL39xYMEsRtmk+/Jir9eA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -561,12 +563,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27ACF517-D2E1-4970-885D-563DC1ECE226}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -585,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -596,7 +598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -607,7 +609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -618,17 +620,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -636,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -647,7 +649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -655,7 +657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -663,7 +665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
